--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/feb-2025.xlsx
@@ -562,7 +562,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +944,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1009,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1074,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1200,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1265,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1330,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1395,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1460,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1525,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1590,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1655,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1720,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1846,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1911,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1976,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2041,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2106,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2171,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2236,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2301,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2366,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2431,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2496,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2622,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2687,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2752,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2817,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2882,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2947,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3012,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3077,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3142,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3207,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3333,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3398,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3463,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
